--- a/modules/Project/ProjectType/Resources/templates/uds-excel-template.xlsx
+++ b/modules/Project/ProjectType/Resources/templates/uds-excel-template.xlsx
@@ -1,37 +1,293 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UDS" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+  <si>
+    <t>Penalty Amount</t>
+  </si>
+  <si>
+    <t>Finance Approval Date</t>
+  </si>
+  <si>
+    <t>Certificate Source Number</t>
+  </si>
+  <si>
+    <t>Modified Employee Number</t>
+  </si>
+  <si>
+    <t>Contractor Assigned Employee Number</t>
+  </si>
+  <si>
+    <t>Order Permit Status</t>
+  </si>
+  <si>
+    <t>Order Permit Position</t>
+  </si>
+  <si>
+    <t>Penalty Percentage</t>
+  </si>
+  <si>
+    <t>Delay Duration</t>
+  </si>
+  <si>
+    <t>Disbursement Status</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Indirect Cost</t>
+  </si>
+  <si>
+    <t>Labor Cost</t>
+  </si>
+  <si>
+    <t>Unpaid Material Cost</t>
+  </si>
+  <si>
+    <t>Paid Material Cost</t>
+  </si>
+  <si>
+    <t>Office Code</t>
+  </si>
+  <si>
+    <t>Current Entity</t>
+  </si>
+  <si>
+    <t>Cost Center Name</t>
+  </si>
+  <si>
+    <t>Cost Center</t>
+  </si>
+  <si>
+    <t>Extract Number</t>
+  </si>
+  <si>
+    <t>Completion Certificate Amount</t>
+  </si>
+  <si>
+    <t>Contractor Approval Date for Completion Certificate</t>
+  </si>
+  <si>
+    <t>Completion Certificate Approval Date</t>
+  </si>
+  <si>
+    <t>Completion Certificate Date</t>
+  </si>
+  <si>
+    <t>Received from Contractor Date</t>
+  </si>
+  <si>
+    <t>Delivered to Contractor Date</t>
+  </si>
+  <si>
+    <t>Action 203 Date</t>
+  </si>
+  <si>
+    <t>Executing Entity</t>
+  </si>
+  <si>
+    <t>Last Action Date</t>
+  </si>
+  <si>
+    <t>Last Action Name</t>
+  </si>
+  <si>
+    <t>Last Action Code</t>
+  </si>
+  <si>
+    <t>Order Permit Type</t>
+  </si>
+  <si>
+    <t>Contract Number</t>
+  </si>
+  <si>
+    <t>Subscriber Type</t>
+  </si>
+  <si>
+    <t>Order Permit Number</t>
+  </si>
+  <si>
+    <t>Order Permit Type Code</t>
+  </si>
+  <si>
+    <t>Contractor</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>مقدار الغرامة</t>
+  </si>
+  <si>
+    <t>تاريخ اعتماد المالية</t>
+  </si>
+  <si>
+    <t>رقم مصدر الشهادة</t>
+  </si>
+  <si>
+    <t>رقم الموظف المعدل</t>
+  </si>
+  <si>
+    <t>رقم الموظف المسند للمقاول</t>
+  </si>
+  <si>
+    <t>حالة أمر العمل</t>
+  </si>
+  <si>
+    <t>موقف أمر العمل</t>
+  </si>
+  <si>
+    <t>نسبة الغرامة</t>
+  </si>
+  <si>
+    <t>مدة التأخير</t>
+  </si>
+  <si>
+    <t>حالة الصرف</t>
+  </si>
+  <si>
+    <t>إجمالي التكلفة</t>
+  </si>
+  <si>
+    <t>التكلفة الغير مباشرة</t>
+  </si>
+  <si>
+    <t>تكلفة العمالة</t>
+  </si>
+  <si>
+    <t>تكلفة المواد الغير مصروفة</t>
+  </si>
+  <si>
+    <t>تكلفة المواد المصروفة</t>
+  </si>
+  <si>
+    <t>رمز المكتب</t>
+  </si>
+  <si>
+    <t>الجهة الحالية</t>
+  </si>
+  <si>
+    <t>اسم مركز التكلفة</t>
+  </si>
+  <si>
+    <t>مركز التكلفة</t>
+  </si>
+  <si>
+    <t>رقم المستخلص</t>
+  </si>
+  <si>
+    <t>مبلغ شهادة الإنجاز</t>
+  </si>
+  <si>
+    <t>تاريخ اعتماد المقاول لشهادة الإنجاز</t>
+  </si>
+  <si>
+    <t>تاريخ اعتماد شهادة الإنجاز</t>
+  </si>
+  <si>
+    <t>تاريخ شهادة الإنجاز</t>
+  </si>
+  <si>
+    <t>تاريخ الاستلام من المقاول</t>
+  </si>
+  <si>
+    <t>تاريخ التسليم للمقاول</t>
+  </si>
+  <si>
+    <t>تاريخ إجراء 203</t>
+  </si>
+  <si>
+    <t>جهة التنفيذ</t>
+  </si>
+  <si>
+    <t>تاريخ آخر إجراء</t>
+  </si>
+  <si>
+    <t>مسمى آخر إجراء</t>
+  </si>
+  <si>
+    <t>رمز آخر إجراء</t>
+  </si>
+  <si>
+    <t>نوع أمر العمل</t>
+  </si>
+  <si>
+    <t>رقم العقد</t>
+  </si>
+  <si>
+    <t>نوع المشترك</t>
+  </si>
+  <si>
+    <t>رقم أمر العمل</t>
+  </si>
+  <si>
+    <t>رمز نوع أمر العمل</t>
+  </si>
+  <si>
+    <t>المقاول</t>
+  </si>
+  <si>
+    <t>المكتب</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,81 +302,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -199,6 +394,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +429,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -408,207 +605,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AL2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="true" style="0"/>
+    <col min="2" max="2" width="22" customWidth="true" style="0"/>
+    <col min="3" max="3" width="22" customWidth="true" style="0"/>
+    <col min="4" max="4" width="22" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22" customWidth="true" style="0"/>
+    <col min="6" max="6" width="22" customWidth="true" style="0"/>
+    <col min="7" max="7" width="22" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22" customWidth="true" style="0"/>
+    <col min="9" max="9" width="22" customWidth="true" style="0"/>
+    <col min="10" max="10" width="22" customWidth="true" style="0"/>
+    <col min="11" max="11" width="22" customWidth="true" style="0"/>
+    <col min="12" max="12" width="22" customWidth="true" style="0"/>
+    <col min="13" max="13" width="22" customWidth="true" style="0"/>
+    <col min="14" max="14" width="22" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22" customWidth="true" style="0"/>
+    <col min="16" max="16" width="22" customWidth="true" style="0"/>
+    <col min="17" max="17" width="22" customWidth="true" style="0"/>
+    <col min="18" max="18" width="22" customWidth="true" style="0"/>
+    <col min="19" max="19" width="22" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22" customWidth="true" style="0"/>
+    <col min="21" max="21" width="22" customWidth="true" style="0"/>
+    <col min="22" max="22" width="22" customWidth="true" style="0"/>
+    <col min="23" max="23" width="22" customWidth="true" style="0"/>
+    <col min="24" max="24" width="22" customWidth="true" style="0"/>
+    <col min="25" max="25" width="22" customWidth="true" style="0"/>
+    <col min="26" max="26" width="22" customWidth="true" style="0"/>
+    <col min="27" max="27" width="22" customWidth="true" style="0"/>
+    <col min="28" max="28" width="22" customWidth="true" style="0"/>
+    <col min="29" max="29" width="22" customWidth="true" style="0"/>
+    <col min="30" max="30" width="22" customWidth="true" style="0"/>
+    <col min="31" max="31" width="22" customWidth="true" style="0"/>
+    <col min="32" max="32" width="22" customWidth="true" style="0"/>
+    <col min="33" max="33" width="22" customWidth="true" style="0"/>
+    <col min="34" max="34" width="22" customWidth="true" style="0"/>
+    <col min="35" max="35" width="22" customWidth="true" style="0"/>
+    <col min="36" max="36" width="22" customWidth="true" style="0"/>
+    <col min="37" max="37" width="22" customWidth="true" style="0"/>
+    <col min="38" max="38" width="22" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Penalty Amount</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Finance Approval Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Certificate Source Number</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Modified Employee Number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Contractor Assigned Employee Number</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Order Permit Status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Order Permit Position</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Penalty Percentage</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Delay Duration</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Disbursement Status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Total Cost</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Indirect Cost</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Labor Cost</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Unpaid Material Cost</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Paid Material Cost</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Office Code</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Current Entity</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Cost Center Name</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Cost Center</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Extract Number</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Completion Certificate Amount</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Contractor Approval Date for Completion Certificate</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Completion Certificate Approval Date</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Completion Certificate Date</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Received from Contractor Date</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Delivered to Contractor Date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Action 203 Date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Executing Entity</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Last Action Date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Last Action Name</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Last Action Code</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Order Permit Type</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Contract Number</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Subscriber Type</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Order Permit Number</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Order Permit Type Code</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
+    <row r="1" spans="1:38" customHeight="1" ht="30">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" customHeight="1" ht="30">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>